--- a/politicians/GiorgiaMeloni_tweets.xlsx
+++ b/politicians/GiorgiaMeloni_tweets.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="200">
   <si>
     <t>Ci lascia a 89 anni Pippo Baudo, uno dei più grandi protagonisti della storia della televisione italiana. Il suo volto e la sua voce hanno accompagnato intere generazioni, regalando emozioni, sorrisi e momenti indimenticabili. Grazie di tutto.</t>
   </si>
@@ -169,12 +169,519 @@
   <si>
     <t>A Don Antonio Coluccia va tutta la mia solidarietà. Chi sfida la criminalità con coraggio e difende la legalità non deve mai sentirsi solo. Siamo al tuo fianco, sempre.</t>
   </si>
+  <si>
+    <t>Nel giorno del 251° Anniversario di fondazione della Guardia di Finanza desidero rivolgere agli uomini e alle donne delle Fiamme Gialle la mia profonda gratitudine, e quella del Governo italiano, per il prezioso lavoro che svolgono ogni giorno con abnegazione e professionalità. Da sempre sono risorsa fondamentale per la difesa della legalità in ambito economico e a loro va il nostro grazie.</t>
+  </si>
+  <si>
+    <t>Il Vertice di oggi a Roma rappresenta un passo fondamentale nell'internazionalizzazione del Piano Mattei. Fin dall'inizio del lancio di questa strategia siamo stati consapevoli che, per raggiungere gli obiettivi ambiziosi che ci eravamo prefissati, fosse necessario lavorare in sinergia con i partner internazionali, a partire dalla Commissione europea.</t>
+  </si>
+  <si>
+    <t>In bocca al lupo a tutti gli studenti che stanno per affrontare la maturità. Forza ragazzi!</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Durante il G7 ho avuto un incontro bilaterale con il Presidente degli Stati Uniti, Donald Trump.
+Abbiamo discusso dei principali dossier internazionali, con particolare attenzione alla situazione in Iran e in Medio Oriente.
+Abbiamo inoltre affrontato il tema delle relazioni economiche tra UE e USA, ribadendo l’importanza di rafforzare la cooperazione transatlantica.
+</t>
+  </si>
+  <si>
+    <t>Nel corso del Vertice G7 di Kananaskis, ho incontrato il Cancelliere della Repubblica Federale di Germania, Friedrich Merz. Durante il colloquio abbiamo confermato la comune volontà di riunire a Roma, a inizio 2026, una nuova edizione del Vertice intergovernativo tra Italia e Germania e di mantenere uno stretto coordinamento su importanti temi dell’agenda UE, come il contrasto all’immigrazione irregolare e la competitività. Abbiamo inoltre avuto uno scambio di vedute sui più recenti sviluppi in Medio Oriente e sul conflitto in Ucraina.</t>
+  </si>
+  <si>
+    <t>Ecco perché riteniamo sbagliato ridurre i tempi per la cittadinanza italiana</t>
+  </si>
+  <si>
+    <t>Profondamente addolorata per il tragico disastro aereo avvenuto ad Ahmedabad. A nome del Governo italiano e mio personale, esprimo le più sincere condoglianze alle famiglie delle vittime e la nostra piena solidarietà al popolo indiano in questo momento di grande dolore.</t>
+  </si>
+  <si>
+    <t>Carlo Legrottaglie, 59 anni. Carabiniere, marito, padre. Gli mancava pochissimo alla pensione, ma ha scelto di intervenire comunque. Come sempre. Per dovere, per coraggio, per quella divisa che portava con onore. A strapparlo alla vita è stata la mano vile di chi fugge dalla legge e spara contro lo Stato. Contro questi criminali non possono esserci sconti, né indulgenze. La sua morte ci ricorda che dietro ogni uniforme c’è una persona, una famiglia, una vita spesa al servizio degli altri. E che colpire un uomo dello Stato significa colpire l’Italia intera. Che la terra ti sia lieve, Carlo.</t>
+  </si>
+  <si>
+    <t>Esprimo il più profondo cordoglio per la morte del Brigadiere Capo dei Carabinieri, Carlo Legrottaglie, ucciso nell’esercizio del suo dovere mentre interveniva a seguito di una rapina, questa mattina a Francavilla Fontana. Il dolore si unisce allo sdegno per l’efferata violenza contro un uomo in divisa, colpito mentre serviva lo Stato e proteggeva i cittadini. Alla sua famiglia, all’Arma dei Carabinieri e a tutti i suoi cari va la mia più sentita vicinanza, personale e del Governo.</t>
+  </si>
+  <si>
+    <t>Sono passati due anni da quando ci ha lasciati Silvio Berlusconi. Voglio ricordarlo come imprenditore visionario e leader politico che ha creduto in un centrodestra unito e in una Nazione forte e autorevole. Questa sua eredità vive nelle battaglie di libertà e di buongoverno che continuiamo a portare avanti.</t>
+  </si>
+  <si>
+    <t>Un anno fa, mentre molti gridavano allo scandalo e ci accusavano di fare propaganda, ho presentato un esposto alla Procura nazionale antimafia e antiterrorismo per denunciare gravi irregolarità nel sistema del “click day” per i permessi di soggiorno. Da allora sono emerse diverse gravi azioni criminali connesse con il traffico dei permessi di soggiorno. Oggi, secondo quanto riportato dalla stampa, arrivano ulteriori conferme inquietanti: identità digitali costruite a tavolino, assunzioni false, legami con i clan, soldi in cambio di accessi illegali nella nostra Nazione. Una rete organizzata e criminale, smascherata grazie al lavoro della magistratura e delle forze dell’ordine. Avevamo ragione. E avevamo il dovere di denunciare. Il Governo continuerà a combattere ogni forma di illegalità legata all’immigrazione, perché l’Italia non è terra di conquista per i trafficanti di permessi e per chi vive di furbizie e scorciatoie. Avanti, senza paura.</t>
+  </si>
+  <si>
+    <t>I numeri parlano chiaro, questo è il Governo che ha raggiunto i risultati migliori nella lotta all’evasione: nel 2024 si è registrato il recupero più alto di sempre, pari a 33,4 miliardi di euro. La nostra visione è molto chiara: chi vuole fare il furbo non ha spazi, ma chi è onesto e si trova in difficoltà merita di essere messo nelle condizioni di poter pagare ciò che deve. Risultato che non è frutto del caso, ma del percorso avviato con la riforma fiscale e con i provvedimenti che questo Governo ha voluto, dal rafforzamento della precompilata al provvedimento contro l’odioso fenomeno delle attività “apri e chiudi”, ovvero quelle attività che eludono il fisco aprendo e chiudendo in breve tempo, non pagando tasse e contributi, per poi riaprire sotto un altro nome. Finora sono state chiuse d’ufficio oltre 10 mila attività di questo tipo, un risultato importante per lo Stato ma ancor più importante per gli imprenditori onesti, che subiscono la concorrenza sleale di queste attività. L’Italia che lavora, che produce, che rispetta le regole è la nostra forza. Insieme stiamo costruendo un futuro nel quale ogni cittadino, ogni lavoratore, ogni imprenditore, possa sentirsi protetto e valorizzato.</t>
+  </si>
+  <si>
+    <t>Con dolore apprendo della tragica notizia che vede coinvolta una scuola a Graz, in Austria, dove uno studente ha ucciso diverse persone e ferito delle altre, alcune di loro molto gravi. La mia vicinanza e quella dell'intero Governo italiano va ai familiari delle vittime, unitamente a un pensiero che desidero rivolgere ai feriti e ai loro cari.</t>
+  </si>
+  <si>
+    <t>Lascia senza parole quanto accaduto al candidato alle presidenziali colombiane, Miguel Uribe Turbay, che si trova in fin di vita dopo essere stato raggiunto da alcuni colpi di arma da fuoco mentre teneva un comizio pubblico a Bogotà. Esprimo la vicinanza mia e di tutto il Governo italiano al senatore Uribe e ai suoi familiari, unitamente alla condanna per questo grave attentato alla democrazia e all’auspicio che venga fatta piena luce sulle responsabilità.</t>
+  </si>
+  <si>
+    <t>Mentre qualcuno a sinistra parla di “isolamento”, noi continuiamo a lavorare per rafforzare il ruolo dell’Italia nel mondo. Una grande Nazione, a cui vogliamo restituire il posto da protagonista che merita.</t>
+  </si>
+  <si>
+    <t>“Marco, poliziotto delle Volanti di Agrigento, libero dal servizio, stava tornando a casa ed è stato fermato da un ragazzo che chiedeva aiuto. Il giovane era alla disperata ricerca del fratello 22enne, che si era allontanato da casa manifestando intenti suicidi, e aveva trovato la sua auto nei pressi di un cavalcavia.
+A poca distanza da lì Marco ha notato la figura di un giovane che aveva scavalcato il guard rail e che si era avvicinato pericolosamente al parapetto della strada sopraelevata.
+Dopo essersi avvicinato ha cominciato con cautela a parlare con lui, scoprendo che si trattava proprio della persona ricercata dai familiari e che, dopo una fortissima delusione d’amore, voleva farla finita.
+Con tempismo, approfittando della distrazione del ragazzo e con il supporto di una pattuglia dei carabinieri, Marco è riuscito ad afferrarlo e a portarlo in salvo per poi affidarlo al personale sanitario”. 
+A Marco e a tutti gli eroi silenziosi in divisa, va la gratitudine del Governo e dell’Italia. Grazie per esserci sempre.</t>
+  </si>
+  <si>
+    <t>Ho incontrato oggi a Palazzo Chigi il Presidente del Consiglio Europeo, Antonio Costa. Al centro del colloquio, la preparazione dei Vertici internazionali in programma nelle prossime settimane e, in particolare, del Consiglio Europeo di giugno. In tale contesto abbiamo discusso i principali temi dell’agenda internazionale, a partire da Ucraina e Medio Oriente, e di quella europea con un focus su competitività, sicurezza e difesa, relazioni transatlantiche e migrazioni.</t>
+  </si>
+  <si>
+    <t>Straordinaria vittoria nel doppio misto al Roland Garros per Sara Errani e Andrea Vavassori, che conquistano così il loro secondo Slam dopo la vittoria negli US Open dello scorso anno. Ancora una volta, avete portato in alto il nostro Tricolore: complimenti campioni, l'Italia è orgogliosa di voi.</t>
+  </si>
+  <si>
+    <t>211 anni al servizio degli italiani. Auguri all’Arma dei Carabinieri, presenza insostituibile per la sicurezza delle nostre comunità, presidio costante di legalità, vicinanza e protezione. Ogni giorno, migliaia di uomini e donne in divisa operano con disciplina, coraggio e spirito di sacrificio per difendere i cittadini, anche nei momenti più difficili. A loro va la nostra gratitudine più profonda. Un pensiero speciale a chi ha perso la vita compiendo il proprio dovere: il loro esempio resta scolpito nella memoria della Nazione. Grazie per tutto ciò che fate. Nei secoli fedele</t>
+  </si>
+  <si>
+    <t>Con l’approvazione definitiva del Decreto Sicurezza al Senato, il Governo compie un passo decisivo per rafforzare la tutela dei cittadini, delle fasce più vulnerabili e dei nostri uomini e donne in divisa. Interveniamo con determinazione contro le occupazioni abusive, accelerando gli sgomberi e proteggendo famiglie, anziani e proprietari onesti, troppo spesso lasciati soli di fronte a ingiustizie intollerabili. Combattiamo le truffe agli anziani, un fenomeno vile che colpisce chi più merita rispetto e protezione. Rafforziamo infine gli strumenti a disposizione delle Forze dell’Ordine, per difendere chi ogni giorno difende i cittadini. Legalità e sicurezza sono pilastri della libertà. E noi continueremo a difenderli con determinazione.</t>
+  </si>
+  <si>
+    <t>Nella serata di ieri, a Roma, ho avuto un lungo incontro con il Presidente della Repubblica francese, Emmanuel Macron, molto utile per rafforzare il dialogo e il coordinamento tra Italia e Francia di fronte alle crescenti sfide comuni. Come Nazioni fondatrici dell’Unione Europea, intendiamo lavorare insieme per un’Europa più sovrana, prospera e orientata alla pace, capace di tutelare i propri cittadini e i propri interessi. Abbiamo riscontrato forti convergenze sull’agenda europea sulla competitività, sulla semplificazione normativa, sul tema degli investimenti pubblici e privati, della transizione energetica con piena neutralità tecnologica e sul sostegno a settori strategici come automotive, siderurgia, intelligenza artificiale, energie decarbonizzate rinnovabili così come nucleare e spazio. Abbiamo inoltre ribadito il nostro fermo sostegno all’Ucraina per raggiungere una soluzione equa e duratura, promuovendo al contempo un potenziamento della difesa europea. L’incontro ci ha permesso anche di affrontare temi di sicurezza cruciali, dal Medio Oriente alla Libia, e di coordinare le posizioni su relazioni transatlantiche e sicurezza economica dell’UE. Abbiamo infine concordato che il prossimo vertice bilaterale si terrà in Francia all’inizio del 2026, per sviluppare ulteriormente la già stretta collaborazione tra le nostre due Nazioni.</t>
+  </si>
+  <si>
+    <t>Il 2 giugno celebriamo la nascita della nostra Repubblica. Un giorno che ci ricorda chi siamo: un popolo fiero, capace di rialzarsi dopo le prove più dure, tenendo saldi i valori della libertà, dell’unità e dell’identità nazionale. Celebrare l’Italia oggi significa onorare chi ha dato la vita per difenderla, e chi ogni giorno la serve con coraggio, dedizione e silenzioso orgoglio. Essere italiani vuol dire appartenere a qualcosa di grande, che va difeso, amato, trasmesso.</t>
+  </si>
+  <si>
+    <t>Le minacce rivolte anche ai figli del Vicepremier Matteo Salvini e del Ministro Matteo Piantedosi dimostrano che non siamo davanti a episodi isolati, ma a una spirale d’odio alimentata da un fanatismo ideologico che ha superato ogni limite. La mia piena solidarietà a Salvini e a Piantedosi. Nessuna divergenza politica, nessuna battaglia ideologica può mai giustificare l’attacco ai figli, ai bambini, alla parte più intima e sacra della vita di una persona.</t>
+  </si>
+  <si>
+    <t>Questo non è scontro politico. Non è nemmeno rabbia. È qualcosa di più oscuro, che racconta un clima malato, un odio ideologico, in cui tutto sembra lecito, anche augurare la morte a un figlio per colpire un genitore. Ed è contro questo clima violento che la politica, tutta, dovrebbe sapersi unire. Perché esistono confini che non devono essere superati mai. E difenderli è una responsabilità che va oltre ogni appartenenza.</t>
+  </si>
+  <si>
+    <t>A Lorenzo, e a tutti gli uomini e le donne in divisa che ogni giorno mettono la vita degli altri davanti alla propria, con coraggio, umanità e spirito di sacrificio, va la nostra gratitudine più profonda. Siete il nostro orgoglio.</t>
+  </si>
+  <si>
+    <t>Martina aveva solo 14 anni. Aveva la vita davanti, i sogni, le amicizie, la scuola. Le è stata tolta con una violenza che lascia senza fiato, uccisa brutalmente da chi diceva di volerle bene. Un delitto spietato, che colpisce nel profondo ogni genitore, ogni cittadino, ogni essere umano. La sua morte ci sconvolge. Ci impone di guardare in faccia un male profondo, che non possiamo né ignorare né normalizzare: la violenza cieca e possessiva che troppo spesso si abbatte sulle donne, anche sulle più giovani. Alla famiglia di Martina va il mio abbraccio, pieno di dolore e vicinanza. Alla Giustizia il compito di intervenire con la massima severità. Alle Istituzioni il dovere di non voltarsi dall’altra parte. Sono molti i provvedimenti che abbiamo approvato finora per tentare di fermare questo male, ma dobbiamo essere consapevoli che le norme non saranno mai sufficienti se non daremo vita ad una profonda svolta culturale e sociale. In questi anni dei passi in avanti sono stati fatti, ma evidentemente non basta. Dobbiamo fare di più, tutti insieme. Per Martina. Per tutte.</t>
+  </si>
+  <si>
+    <t>Con profondo dolore apprendo della scomparsa di Silvia Mattei, una donna che ha portato sulle spalle il peso di una tragedia, quella del Rogo di Primavalle, nella quale persero la vita i suoi fratelli Stefano e Virgilio. Testimone di un dolore che non si spegne, ma anche di una dignità che non si piega. Per quell'atto di inaudita violenza politica che ha segnato la storia della nostra Nazione. Esprimo la mia vicinanza alla famiglia Mattei e a chi, come loro, ha sofferto per le ferite di quegli anni bui. Che Silvia possa riposare in pace, riunita ai suoi cari. L’Italia non dimentica.</t>
+  </si>
+  <si>
+    <t>Le parole pronunciate dalla Commissione contro il razzismo e l’intolleranza del Consiglio d’Europa, che accusano le Forze di Polizia italiane di razzismo, sono semplicemente vergognose. Tutti conoscono i numerosi episodi in cui agenti delle Forze dell’Ordine vengono aggrediti, spesso da immigrati irregolari, mentre svolgono il proprio dovere con coraggio, dedizione e rispetto della legge. Purtroppo non è la prima volta che alcuni organismi del Consiglio d’Europa – finanziato anche con i soldi dei cittadini italiani – si abbandonano a giudizi infondati, frutto di un approccio ideologico e di pregiudizi evidenti. L’Italia fu, nel 1949, tra i dieci Stati fondatori del Consiglio d’Europa, nato nel dopoguerra per difendere la democrazia, i diritti umani e lo Stato di diritto. Eppure oggi quello spirito originario sembra smarrito, sostituito da dichiarazioni sempre più faziose e lontane dalla realtà. Noi continueremo a difendere chi, ogni giorno, garantisce la sicurezza dei cittadini italiani. Con orgoglio.</t>
+  </si>
+  <si>
+    <t>Contestare e correggere l’approccio ideologico alla transizione energetica è un atto di responsabilità. Negli anni sono stati prodotti enormi danni, senza che arrivassero i vantaggi promessi. Serve il coraggio di dirlo e di rimettere al centro la realtà.</t>
+  </si>
+  <si>
+    <t>Un passo in più per il futuro di Caivano</t>
+  </si>
+  <si>
+    <t>Villa Doria Pamphilj, il mio intervento alla presentazione ufficiale dei trofei della Louis Vuitton Cup e dell'America's Cup.</t>
+  </si>
+  <si>
+    <t>Dicevano che era inutile, sbagliato, persino disumano. E invece, grazie alle nuove norme introdotte dal Decreto Sicurezza, in Italia sono già stati eseguiti i primi sgomberi immediati di immobili occupati abusivamente. Un risultato concreto, reso possibile da procedure che consentono finalmente un intervento veloce e il ripristino rapido della legalità. Avanti così, per tutelare i più deboli e difendere la proprietà privata.</t>
+  </si>
+  <si>
+    <t>Il 23 maggio è la Giornata della Legalità, in memoria delle vittime della mafia. Ricordiamo Giovanni Falcone, Francesca Morvillo, gli agenti della scorta, tutti coloro che hanno sacrificato la vita per difendere i valori della legalità. E con loro, ogni vittima caduta per mano mafiosa. Il loro esempio e il loro ricordo continuano a guidare la nostra azione. Anche in loro nome, il Governo è e sarà sempre in prima linea nella lotta contro ogni forma di criminalità. Senza tregua, senza compromessi. Non dimentichiamo.</t>
+  </si>
+  <si>
+    <t>Ho ricevuto oggi a Palazzo Chigi il Primo Ministro della Repubblica di Bulgaria, Rossen Jeliazkov. Il colloquio ha permesso di registrare la comune volontà di approfondire le relazioni bilaterali in settori strategici quali infrastrutture e trasporti, energia, interconnessioni e difesa. Nel corso delle discussioni è anche emersa un’ampia consonanza di vedute tra sui principali temi europei, a partire dalla politica di coesione, dall’allargamento e dalla ricerca di soluzioni innovative alle migrazioni irregolari. In relazione ai principali dossier di politica internazionale, ci siamo soffermati sul conflitto in Ucraina, confermando il sostegno agli sforzi in corso per il raggiungimento di una pace giusta e duratura.</t>
+  </si>
+  <si>
+    <t>Ho avuto oggi una conversazione telefonica con il Santo Padre sui prossimi passi da compiere per costruire una pace giusta e duratura in Ucraina.
+Il colloquio fa seguito alla telefonata di ieri con il Presidente Trump e con altri leader europei, nel corso della quale mi è stato chiesto di verificare la disponibilità della Santa Sede a ospitare i negoziati. Trovando nel Santo Padre conferma della disponibilità ad accogliere in Vaticano i prossimi colloqui tra le parti, ho espresso profonda gratitudine per la sua apertura e per il suo incessante impegno a favore della pace.
+Nel corso della giornata, mi sono inoltre confrontata telefonicamente anche con il Presidente Zelensky, il Presidente Macron, il Presidente Stubb, il Primo Ministro Starmer, il Cancelliere Merz e la Presidente della Commissione Europea von der Leyen. Abbiamo concordato di mantenere uno stretto coordinamento tra i partner in vista di un nuovo round di negoziati finalizzato a un cessate il fuoco e a un accordo di pace in Ucraina.</t>
+  </si>
+  <si>
+    <t>Il Tricolore non è un ornamento. È il simbolo vivo dell’unità nazionale, della nostra storia e dei valori fondanti della Repubblica. Porta con sé il sacrificio di chi ha costruito la nostra libertà e la responsabilità di chi oggi è chiamato a rappresentare e servire l’Italia. Onorare il Tricolore significa onorare la Patria, con rispetto, dedizione e orgoglio. Sempre.</t>
+  </si>
+  <si>
+    <t>Addio a Nino Benvenuti, campione straordinario e simbolo di un’Italia fiera, coraggiosa, capace di rialzarsi. È stato uno dei più grandi pugili della nostra storia, ma anche molto di più: profondamente legato alle sue radici istriane, è stato un testimone instancabile della tragedia delle foibe e dell’esodo giuliano-dalmata, contribuendo a scrivere una storia che non era stata raccontata. Alla sua famiglia e a tutti coloro che gli hanno voluto bene va il mio pensiero commosso. Grazie, Nino, per i tuoi combattimenti sul ring e per quelli in difesa della verità. L’Italia non ti dimenticherà.</t>
+  </si>
+  <si>
+    <t>Al termine della telefonata tra il Presidente Trump e il Presidente Putin ho avuto una nuova conversazione telefonica insieme al Presidente francese, Emmanuel Macron, al Cancelliere tedesco, Friedrich Merz, al Presidente finlandese, Alexander Stubb, alla Presidente della Commissione Europea, Ursula von der Leyen e al Presidente ucraino, Volodymyr Zelensky, con il Presidente degli Stati Uniti. Si lavora per un immediato avvio dei negoziati tra le parti che possano condurre il prima possibile a un cessate il fuoco e costruire le condizioni per una pace giusta e duratura in Ucraina. Al riguardo, è stata considerata positivamente la disponibilità del Santo Padre ad ospitare i colloqui presso il Vaticano. L’Italia è pronta a fare la sua parte per facilitare i contatti e lavorare per la pace.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">A nome del Governo italiano, porgo i miei complimenti a @NicusorDanRO per la sua elezione a Presidente della Romania. Sono fiduciosa che potremo costruire una collaborazione costruttiva, al fine di rafforzare la cooperazione bilaterale tra le nostre Nazioni e con l’obiettivo comune di promuovere pace, stabilità e prosperità per i nostri popoli e per l’Europa.
+</t>
+  </si>
+  <si>
+    <t>Nella tarda serata di ieri ho avuto una conversazione telefonica con il Presidente degli Stati Uniti d’America, Donald J. Trump, insieme ai Leader di Regno Unito, Keir Starmer, Francia, Emmanuel Macron, e Germania, Friedrich Merz, per consultazioni prima dell’annunciata telefonata che il Presidente Trump avrà oggi con il Presidente Putin. Ho voluto innanzitutto ribadire il sostegno dell’Italia, insieme ai partner europei e occidentali, agli sforzi del Presidente Trump per una pace giusta e duratura in Ucraina, sottolineando l’importanza di un cessate il fuoco immediato e incondizionato. Ho espresso apprezzamento per la disponibilità dimostrata ancora una volta da parte ucraina a favore del dialogo e ho reiterato l’auspicio che Mosca si impegni seriamente attraverso contatti diretti tra Leader in un negoziato che conduca alla pace.</t>
+  </si>
+  <si>
+    <t>Spero che la giornata di oggi possa essere un primo incontro e un nuovo inizio.</t>
+  </si>
+  <si>
+    <t>Un confronto costruttivo oggi a Palazzo Chigi con il vicepresidente degli Stati Uniti J.D. Vance e la presidente della Commissione europea Ursula von der Leyen. L’Italia intende fare la sua parte per rilanciare il dialogo tra Unione Europea e Stati Uniti: due realtà chiamate ad affrontare insieme le grandi sfide globali. Libertà, democrazia e centralità della persona sono i valori comuni su cui costruire un futuro più sicuro, prospero e stabile. Orgogliosa di questo passo in avanti per l'unità dell'Occidente.</t>
+  </si>
+  <si>
+    <t>Dopo la splendida vittoria di ieri, oggi un’altra grande soddisfazione per il tennis italiano: Sara Errani e Jasmine Paolini conquistano nuovamente il titolo del doppio agli Internazionali d’Italia. Bravissime</t>
+  </si>
+  <si>
+    <t>Oggi a Palazzo Chigi, una giornata di incontri e lavoro su dossier strategici per l’Italia. Avanti con determinazione.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Complimenti a Jasmine #Paolini per una vittoria straordinaria agli Internazionali di Roma.
+Un’impresa che entra nella storia dello sport italiano e rende orgogliosa tutta la Nazione.
+</t>
+  </si>
+  <si>
+    <t>Oggi al Vertice della Comunità Politica Europea a Tirana ho ribadito una verità semplice ma fondamentale: il futuro dell’Europa non si affida al caso né ad altri, ma dipende da noi. Dobbiamo difendere con determinazione le nostre radici, la libertà, la dignità e l’identità dei nostri popoli, valori che rappresentano il fondamento della nostra civiltà.</t>
+  </si>
+  <si>
+    <t>Sul disagio giovanile faccio appello a tutte le forze politiche: uniamoci per affrontare una battaglia della massima importanza.</t>
+  </si>
+  <si>
+    <t>Questo Governo sarà sempre al fianco dei nostri uomini e delle nostre donne in divisa. E lo sta dimostrando con i fatti.</t>
+  </si>
+  <si>
+    <t>Sono orgogliosa di annunciare che l’America’s Cup si disputerà, per la prima volta nella storia, in Italia. Sarà Napoli la città che ospiterà nel 2027 la trentottesima edizione del torneo velico più famoso e prestigioso al mondo, un evento globale che coinvolge milioni di appassionati e rappresenta una sintesi unica tra tradizione, innovazione tecnologica, eccellenza ingegneristica e spirito competitivo. Ringrazio il Ministro per lo Sport e i Giovani Andrea Abodi, il Ministro dell’Economia Giancarlo Giorgetti, il Sindaco di Napoli Gaetano Manfredi, Sport e Salute e tutti coloro che hanno lavorato, con passione e determinazione, per raggiungere questo grande risultato. La scelta del capoluogo partenopeo contribuirà a rafforzare il rinnovato protagonismo del Sud, che in questi anni ha saputo riscoprire il suo dinamismo e il suo orgoglio, registrando una crescita del PIL e dell’occupazione superiore alla media nazionale. L’organizzazione dell’America’s Cup a Napoli consentirà, inoltre, di accelerare l’imponente piano di riqualificazione e rigenerazione avviato dal Governo per trasformare l’area di Bagnoli in un moderno polo turistico, balneare e commerciale. La scelta dell’Italia è una scelta che ci inorgoglisce, perché è un riconoscimento all’identità stessa della nostra Nazione. Senza il mare, infatti, noi non saremmo ciò che siamo. Il mare è storia, identità, cultura ma anche un pezzo insostituibile del nostro sistema produttivo ed economico, grazie alla posizione di leadership che ricopriamo nella nautica, nella cantieristica, nell’industria armatoriale, nella crocieristica e in tanti altri ambiti connessi alla blue economy. Non vediamo l'ora di accogliere l’America’s Cup. L'Italia sarà all'altezza di questa sfida, e dimostrerà ancora una volta al mondo di cosa è capace.</t>
+  </si>
+  <si>
+    <t>Stiamo lavorando per riscrivere il nuovo Piano Sanitario Nazionale, con serietà e visione, per garantire a tutti i cittadini una sanità più equa, efficiente e moderna. Elly, collaborerete per il bene dell’Italia o continuerete a tifare contro sperando nei sondaggi?</t>
+  </si>
+  <si>
+    <t>Saranno i cittadini a giudicare, sempre.</t>
+  </si>
+  <si>
+    <t>La mia risposta a Giuseppe Conte nel corso del Question Time alla Camera dei Deputati</t>
+  </si>
+  <si>
+    <t>Buongiorno. Oggi, dalle ore 16, sarò alla Camera dei Deputati per il Question Time. Seguitemi se vi va.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Desidero porgere i miei più sinceri auguri al Primo Ministro @ediramaal per la sua riconferma alla guida del governo albanese. La profonda amicizia e la collaborazione strategica che lega le nostre due Nazioni si è ulteriormente rafforzata grazie a iniziative comuni, frutto di un dialogo costruttivo e di una volontà condivisa di affrontare le sfide globali con soluzioni innovative. Continueremo a lavorare per consolidare ulteriormente il legame tra i nostri due Governi e per raggiungere gli obiettivi condivisi, incluso il rafforzamento della stabilità nei Balcani e il progresso del percorso europeo dell’Albania.
+</t>
+  </si>
+  <si>
+    <t>Buona Festa della Mamma!</t>
+  </si>
+  <si>
+    <t>In occasione della 96ª Adunata Nazionale degli Alpini a Biella e del 72° Raduno Nazionale dei Bersaglieri a Marsala, rivolgo il mio saluto più sentito, personale e a nome del Governo, a tutti i partecipanti di queste celebrazioni.
+Coraggio, dedizione, spirito di sacrificio, amore per la Patria: sono i valori che da sempre vi contraddistinguono e che vi rendono motivo d’orgoglio per l’Italia intera.
+Siete fratelli nella fierezza delle vostre tradizioni, uniti nella fedeltà al Tricolore.
+Viva gli Alpini, viva i Bersaglieri, viva l’Italia!</t>
+  </si>
+  <si>
+    <t>Oggi ricordiamo Aldo Moro e Peppino Impastato, due figure diverse, che hanno segnato la storia recente d'Italia, accumunate da un tragico destino: il 9 maggio 1978, persero la vita per mano di due delle forze oscure - le Brigate Rosse e Cosa Nostra - che hanno insanguinato la nostra Nazione negli anni bui del terrorismo e della mafia. Aldo Moro, uomo delle Istituzioni, rapito e ucciso da chi voleva piegare lo Stato con la violenza e l’intolleranza ideologica. Peppino Impastato, assassinato per aver denunciato e sfidato a viso aperto e senza paura il potere mafioso. Due simboli, caduti per altro nel pieno di quegli “anni di piombo” che hanno segnato l’Italia con il sangue di troppi innocenti: servitori dello Stato, rappresentanti delle Istituzioni, cittadini, giovani di diverse idee politiche. Nel Giorno della Memoria dedicato alle vittime del terrorismo, rinnoviamo il nostro impegno a difendere la libertà, la giustizia e la legalità. La loro eredità ci ricorda che l’Italia non si piega davanti a chi semina morte e paura. Onoriamo il loro sacrificio, costruendo ogni giorno una Nazione più forte, unita e libera. No alla violenza politica, di qualsiasi colore, e all'oppressione mafiosa.</t>
+  </si>
+  <si>
+    <t>Rivolgo i più sinceri auguri a Papa Leone XIV per l’inizio del suo pontificato. In un tempo segnato da conflitti e inquietudini, le sue parole dalla Loggia delle Benedizioni sono un richiamo potente alla pace, alla fraternità e alla responsabilità. Un’eredità spirituale che si raccoglie nel solco tracciato da Papa Francesco, e che l’Italia guarda con rispetto e speranza.</t>
+  </si>
+  <si>
+    <t>Question Time, in diretta dal Senato della Repubblica</t>
+  </si>
+  <si>
+    <t>Oggi, dalle ore 13.30, sarò al Senato della Repubblica per il Question Time. Potrete seguire l’evento in diretta sui miei canali YouTube e X. Buona giornata.</t>
+  </si>
+  <si>
+    <t>Congratulazioni a @_FriedrichMerz per la sua elezione a Cancelliere federale tedesco.
+La cooperazione tra Italia e Germania è cruciale per affrontare le sfide globali.
+Le nostre due Nazioni, principali economie manifatturiere europee, possono dare un contributo decisivo al rilancio della competitività – a partire dal settore automobilistico – e alla costruzione di partenariati equi con l’Africa, oltre che al contrasto all’immigrazione irregolare.</t>
+  </si>
+  <si>
+    <t>L’ennesimo indegno oltraggio a un monumento dedicato a Sergio Ramelli ed Enrico Pedenovi non è solo un atto ignobile: è il segno che l’odio ideologico, quello che li ha assassinati, non è mai davvero scomparso. Chi infanga la memoria di due italiani uccisi per le loro idee dimostra quanto sia ancora necessario difendere la verità contro l’intolleranza. Ricordarli non è solo un dovere. È un gesto di giustizia verso la storia, che nessuna vigliaccheria potrà cancellare.</t>
+  </si>
+  <si>
+    <t>Un’altra magnifica impresa per la Pallavolo italiana! Grandissima Imoco Conegliano, che si conferma regina d’Europa grazie alla vittoria della Champions League femminile, con la quale completa il Grande Slam. Complimenti anche a Scandicci e Milano per il podio tutto italiano: è la prima volta nella storia. Grazie alle nostre atlete per aver portato il Tricolore così in alto, con talento e passione!</t>
+  </si>
+  <si>
+    <t>Nel 164° anniversario della sua costituzione, desidero esprimere – a nome mio e del Governo – profonda gratitudine alle donne e agli uomini dell’Esercito Italiano che ogni giorno servono l’Italia con coraggio, impegno e spirito di sacrificio, in Patria e nelle missioni internazionali. A loro va il nostro ringraziamento per il contributo essenziale alla sicurezza e alla difesa della Nazione. Un pensiero commosso è rivolto a chi ha perso la vita indossando l’uniforme: il loro esempio vive nella memoria di tutti noi. Grazie a ciascuno di voi. Viva l’Esercito Italiano.</t>
+  </si>
+  <si>
+    <t>Dalla mia intervista di oggi all’Adnkronos  “Alla fine dei 5 anni per quali risultati vuole che il suo governo venga ricordato?” Voglio realizzare per intero il programma del Centrodestra e potermi ripresentare agli elettori dicendo la cosa più banale su cui i politici andrebbero giudicati: ve lo avevamo promesso, lo abbiamo fatto. Vale per l’economia, per l’immigrazione, per la sicurezza, per il sostegno alla famiglia, per le riforme istituzionali, per la politica estera. E vale per il lavoro, perché vogliamo essere ricordati come il Governo che ha aumentato il lavoro, ridotto il precariato e messo al centro la sicurezza sul posto di lavoro. Proprio su questo sono fiera che il Governo abbia reperito, insieme all’INAIL, ulteriori 650 milioni su questo tema, che sommati ai 600 milioni già previsti quest’anno, portano a oltre un miliardo e 250 milioni la dotazione disponibile. Ci confronteremo l’8 maggio con le parti sociali per discutere delle proposte del governo e ascoltare quelle che ci verranno sottoposte.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Il lavoro è uno dei pilastri su cui questo Governo ha fondato la sua azione. In due anni e mezzo sono stati creati oltre un milione di posti di lavoro e il numero complessivo degli occupati ha raggiunto il massimo storico: più di 24 milioni e 300 mila. Anche l’occupazione femminile ha toccato il livello più alto di sempre. La disoccupazione è ai minimi da 18 anni a questa parte. Un impegno concreto che continua anche sul fronte della sicurezza, con nuove risorse, più controlli, incentivi e una forte spinta sulla prevenzione e sulla formazione. C’è ancora tanto da fare, ma la direzione è chiara. Buon </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>#PrimoMaggio</t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+      </rPr>
+      <t xml:space="preserve"> a chi lavora, a chi cerca un’occasione, a chi non si arrende e ogni giorno contribuisce – in tanti modi diversi – alla crescita dell’Italia.</t>
+    </r>
+  </si>
+  <si>
+    <t>Domani è la Festa dei Lavoratori e anche quest’anno il Governo ha deciso di celebrarla con i fatti, perché crediamo che questo sia il modo migliore per ringraziare gli italiani che ogni giorno contribuiscono a far grande la nostra Nazione. Ascoltate.</t>
+  </si>
+  <si>
+    <t>Congratulazioni a @MarkJCarney per il successo elettorale. Sono certa che Italia e Canada sapranno approfondire ulteriormente il loro partenariato di successo. Siamo pronti a lavorare insieme per il rafforzamento dei rapporti bilaterali e della cooperazione di fronte alle principali sfide internazionali, che troverà nel Vertice G7 che il Canada ospiterà a giugno un importante momento di confronto e dialogo.</t>
+  </si>
+  <si>
+    <t>Vertice Intergovernativo Italia-Turchia: le mie dichiarazioni alla stampa.</t>
+  </si>
+  <si>
+    <t>Il 29 aprile ricorrono 50 anni dalla morte di Sergio Ramelli. Il mio videomessaggio per l’evento in suo ricordo</t>
+  </si>
+  <si>
+    <t>Oggi l’Italia celebra l’ottantesimo Anniversario della Liberazione. In questa giornata, la Nazione onora la sua ritrovata libertà e riafferma la centralità di quei valori democratici che il regime fascista aveva negato e che da settantasette anni sono incisi nella Costituzione repubblicana. La democrazia trova forza e vigore se si fonda sul rispetto dell’altro, sul confronto e sulla libertà e non sulla sopraffazione, l’odio e la delegittimazione dell’avversario politico. Oggi rinnoviamo il nostro impegno affinché questa ricorrenza possa diventare sempre di più un momento di concordia nazionale, nel nome della libertà e della democrazia, contro ogni forma di totalitarismo, autoritarismo e violenza politica.</t>
+  </si>
+  <si>
+    <t>Con l’approvazione definitiva al Senato del Decreto Bollette, il Governo mette in campo misure concrete per sostenere famiglie e imprese di fronte al caro energia. Lo facciamo attraverso un investimento di circa 3 miliardi, destinato ad alleggerire le bollette, promuovere l’efficienza energetica, tutelare i più vulnerabili e chi produce. In particolare, per le famiglie con un Isee fino a 25mila euro, prevediamo un contributo straordinario di 200 euro. Per le famiglie con redditi più bassi che già percepiscono il bonus bollette, si tratta di un contributo aggiuntivo, con il beneficio complessivo che può raggiungere i 500 euro. Non ci fermeremo qui: continueremo a lavorare con serietà e determinazione per contrastare il caro energia e aiutare chi ha bisogno.</t>
+  </si>
+  <si>
+    <t>Camera dei Deputati, il mio intervento alla Commemorazione di Sua Santità Papa Francesco a Camere riunite.</t>
+  </si>
+  <si>
+    <t>Profondamente addolorata per l’attacco terroristico avvenuto oggi in India, che ha causato numerose vittime. L’Italia esprime vicinanza alle famiglie colpite, ai feriti, al Governo e a tutto il popolo indiano.</t>
+  </si>
+  <si>
+    <t>Papa Francesco è tornato alla casa del Padre. Una notizia che ci addolora profondamente, perché ci lascia un grande uomo e un grande pastore. Ho avuto il privilegio di godere della sua amicizia, dei suoi consigli e dei suoi insegnamenti, che non sono mai venuti meno neanche nei momenti di prova e di sofferenza. Nelle meditazioni della Via Crucis, ci ha ricordato la potenza del dono, che fa rifiorire tutto ed è capace di riconciliare ciò che agli occhi dell’uomo è inconciliabile. E ha chiesto al mondo, ancora una volta, il coraggio di un cambio di rotta, per percorrere una strada che “non distrugge, ma coltiva, ripara, custodisce”. Cammineremo in questa direzione, per ricercare la strada della pace, perseguire il bene comune e costruire una società più giusta e più equa. Il suo magistero e la sua eredità non andranno perduti. Salutiamo il Santo Padre con il cuore colmo di tristezza, ma sappiamo che ora è nella pace del Signore.</t>
+  </si>
+  <si>
+    <t>Buona Pasqua a tutti voi. Che sia un giorno di serenità, speranza e felicità da condividere con le persone che amate. Un abbraccio sincero, ovunque voi siate.</t>
+  </si>
+  <si>
+    <t>Oggi, a Palazzo Chigi, ho ricevuto il Vicepresidente degli Stati Uniti d’America J.D. Vance. Italia e Stati Uniti continuano a rafforzare la loro cooperazione su tutti i principali dossier internazionali. Un’amicizia solida, una partnership strategica.</t>
+  </si>
+  <si>
+    <t>Grazie, Presidente Trump! La collaborazione tra Italia e Stati Uniti si fonda su valori comuni e una lunga amicizia. Continueremo a lavorare insieme per rafforzare il legame tra i nostri popoli e affrontare con determinazione le sfide globali.</t>
+  </si>
+  <si>
+    <t>Lavorare insieme per costruire un Occidente più forte. Oggi a Washington ho incontrato il Presidente @realDonaldTrump. Un confronto leale e costruttivo su temi strategici: dalla sicurezza alla difesa, dalla lotta all’immigrazione illegale ai rapporti commerciali. Ho colto l’occasione per invitarlo a Roma, e sono lieta che abbia accettato. Sarà un’ulteriore occasione per rafforzare il dialogo tra le nostre Nazioni. L’Italia è sempre più protagonista in uno scenario internazionale che cambia rapidamente. E oggi, anche grazie al lavoro fatto in questi anni, il nostro punto di vista viene ascoltato e rispettato. Il legame tra Italia e Stati Uniti resta solido, vitale e decisivo per affrontare insieme le grandi sfide globali</t>
+  </si>
+  <si>
+    <t>Accolgo con grande soddisfazione la proposta di lista UE Paesi sicuri di origine presentata dalla Commissione europea e che ricomprende, tra gli altri, anche Bangladesh, Egitto e Tunisia. Ritengo altrettanto positiva la proposta di anticipare l’entrata in vigore di alcune componenti del Patto Migrazione e Asilo, in particolare la possibilità di designare Paesi sicuri di origine con eccezioni territoriali e per determinate categorie e di applicare il criterio del 20%. Si tratta infatti di fattispecie che consentono di attivare le procedure accelerate di frontiera ai migranti che arrivano da determinate Nazioni, come previsto dal Protocollo Italia-Albania. È un’ulteriore conferma della bontà della direzione tracciata dal Governo italiano in questi anni e del sostegno di sempre più Nazioni europee. L’Italia ha svolto e sta svolgendo un ruolo decisivo per cambiare l’approccio europeo nei confronti del governo dei flussi migratori. Se oggi anche in Europa ci si pone come priorità la difesa dei confini esterni, il contrasto all’immigrazione irregolare di massa, il rafforzamento della politica dei rimpatri e l’attuazione di partenariati paritari con i Paesi di origine e transito, lo si deve per buona parte alla determinazione e alla caparbietà dell’Italia. I fatti dimostrano che avevamo ragione e che siamo sulla buona strada.</t>
+  </si>
+  <si>
+    <t>Stefano e Virgilio Mattei furono bruciati vivi nella loro casa. Due ragazzi innocenti, uccisi dalla furia ideologica e dall’odio politico. Ricordarli oggi non è solo un dovere morale: è un atto di giustizia verso la verità e verso la storia. Perché nulla si costruisce sull’odio. E perché certi orrori non devono accadere mai più. Non dimentichiamo.</t>
+  </si>
+  <si>
+    <t>Al Presidente Mattarella i miei più sentiti auguri per un pronto e pieno ristabilimento. L’Italia lo attende presto, con la forza e la dedizione di sempre.</t>
+  </si>
+  <si>
+    <t>A 21 anni dalla sua uccisione, ricordiamo Fabrizio Quattrocchi. Con le sue parole, “vi faccio vedere come muore un italiano”, ha dimostrato coraggio e orgoglio nazionale. L’Italia non dimentica.</t>
+  </si>
+  <si>
+    <t>Oggi ricordiamo la nascita di Adriano Olivetti, nato l’11 aprile 1901, un uomo che ha profondamente incarnato il genio italiano. La sua visione del fare impresa - con al centro la persona e la sua crescita umana, professionale e culturale, in cui il profitto è uno strumento da reinvestire a beneficio della comunità - è ancora oggi un esempio che ci ispira.</t>
+  </si>
+  <si>
+    <t>Oggi ho incontrato Sua Maestà la Regina Rania di Giordania. Il colloquio ha evidenziato l’eccellente cooperazione bilaterale tra Italia e Giordania, incluso nei settori dell’istruzione e della tutela della famiglia e dell’infanzia, rispetto ai quali la Regina Rania ha avviato numerose iniziative a livello nazionale e globale. Nel corso del bilaterale abbiamo inoltre avviato un approfondito scambio sulla situazione umanitaria a Gaza, valorizzando l’importante cooperazione già esistente tra le nostre Nazioni per portare assistenza alla popolazione civile, in particolare attraverso le iniziative Food for Gaza e Sky Hope.</t>
+  </si>
+  <si>
+    <t>È stato per me un onore accogliere oggi a Villa Pamphilj Sua Maestà, Re Carlo III. Un incontro che ha permesso di sottolineare la storica amicizia tra le nostre Nazioni, che auspichiamo si possa rafforzare sempre più.</t>
+  </si>
+  <si>
+    <t>Oggi onoriamo le 309 vite spezzate dal terremoto che ha colpito L’Aquila e l’Abruzzo nel 2009. Ricordiamo l’impegno di tutti coloro che, con straordinario spirito di solidarietà e abnegazione, hanno dato il massimo per affrontare l’emergenza e hanno contribuito alla rinascita dei territori colpiti. Rendiamo omaggio al popolo abruzzese, che ha sempre affrontato le sfide degli ultimi anni con forza e determinazione, senza mai tirarsi indietro di fronte alle difficoltà. Siete un esempio per tutta l’Italia. 16 anni fa siamo stati feriti, però abbiamo saputo rialzarci e tornare più forti. L’Aquila a l’Abruzzo stanno rinascendo grazie ad un lavoro di squadra straordinario e di cui siamo tutti orgogliosi. Continueremo a lavorare con questo spirito, per completare la ricostruzione. L’Abruzzo è e rimarrà sempre nel cuore di ognuno di noi.</t>
+  </si>
+  <si>
+    <t>Approvato oggi in Consiglio dei Ministri il nuovo decreto sicurezza: più strumenti e tutele per le Forze dell’Ordine, tempi più rapidi per liberare gli immobili occupati illegalmente, maggior rigore contro chi delinque e molte altre misure a tutela della sicurezza dei cittadini. Avevamo promesso un’Italia più sicura e stiamo mantenendo quella promessa. Il Governo continuerà a lavorare con determinazione su questa strada.</t>
+  </si>
+  <si>
+    <t>La mia solidarietà al Sottosegretario alla Giustizia, Andrea Delmastro, oggetto di gravissime minacce da parte di un affiliato alla criminalità organizzata. Queste intimidazioni confermano che la direzione intrapresa dal Governo nella lotta alla criminalità è quella giusta. Conosco bene Andrea e so che non si farà certo intimidire, ma andrà avanti con la determinazione di sempre. Lo Stato non si piega. E questo Governo non arretra di un passo nella battaglia contro la criminalità organizzata.</t>
+  </si>
+  <si>
+    <t>Oggi, a Palazzo Chigi, la cerimonia per il conferimento del Premio “Maestro dell’Arte della Cucina Italiana”: un doveroso riconoscimento nei confronti di chi, con arte e maestria, porta in alto l'eccellenza culinaria italiana nel mondo. Grazie al Ministro Lollobrigida, che ha promosso l'istituzione di questo premio, e a tutti i Maestri, i rappresentanti delle categorie, gli studenti e i docenti degli istituti alberghieri e agrari che hanno scritto insieme a noi questa bella pagina di orgoglio, identità e amore per la nostra Nazione</t>
+  </si>
+  <si>
+    <t>Vent’anni fa, il 2 aprile 2005, San Giovanni Paolo II passava dalla terra al cielo. La sua forza spirituale, il suo amore per la libertà e la sua capacità di avvicinare alla fede uomini e donne di ogni generazione e latitudine restano vivi nella memoria e nel cuore di miliardi di persone. Sono onorata di aver incontrato e conosciuto una figura così straordinaria che con la sua vita, le sue azioni e il suo esempio ha plasmato il Novecento e cambiato la storia. Grazie di tutto, San Giovanni Paolo II.</t>
+  </si>
+  <si>
+    <t>Quando questo Governo ha iniziato il proprio mandato, nell’ottobre del 2022, il numero di occupati in Italia era di 23 milioni e 231 mila. Oggi, la rilevazione dell’Istat ci dice che, a febbraio 2025, quel numero era già salito a 24 milioni e 332 mila: oltre un milione di occupati in più. È il frutto del lavoro di tanti, in primis delle imprese. Come Governo abbiamo cercato di fare la nostra parte: in poco più di due anni, abbiamo lavorato con l’obiettivo di creare opportunità, sostenere le imprese e ridare dignità al lavoro. È la nostra idea di Italia che prende forma, passo dopo passo. Molto c’è ancora da fare e non ci fermeremo, perché il lavoro è la prima risposta a chi vuole una Nazione più forte e un futuro più prospero.</t>
+  </si>
+  <si>
+    <t>Su Marine Le Pen ribadisco quanto già detto a “Il Messaggero”: Nessuno che creda davvero nella democrazia può gioire di una sentenza che colpisce il leader di un grande partito, privando milioni di cittadini della loro rappresentanza.</t>
+  </si>
+  <si>
+    <t>Il nostro più grande obiettivo: consegnare a chi verrà dopo di noi un’Italia migliore di quella che abbiamo ereditato. Un’Italia che torni a indicare la rotta, consapevole di poter ancora stupire il mondo.</t>
+  </si>
+  <si>
+    <t>Sono devastanti le immagini che ci arrivano dal Sud-Est asiatico dove una forte scossa di terremoto, con epicentro in Myanmar, ha provocato centinaia di morti e feriti. La mia solidarietà, e quella del Governo italiano, alle popolazioni colpite e il mio più sincero sentimento di vicinanza alle famiglie delle vittime e delle persone rimaste coinvolte in questa tragedia.</t>
+  </si>
+  <si>
+    <t>La sesta Relazione al Parlamento sullo stato di attuazione del Piano Nazionale di Ripresa e Resilienza conferma il primato europeo dell’Italia nella sua realizzazione, per numero di obiettivi conseguiti, per risorse complessive ricevute e per numero di richieste di pagamento formalizzate e incassate. Il Governo, le Amministrazioni titolari, le Prefetture e tutti i soggetti attuatori continueranno a lavorare, con costanza e determinazione, per portare a compimento tutti gli investimenti e le riforme. Lo faremo con lo stesso rigore, la stessa passione e lo stesso spirito di abnegazione che ci hanno permesso di diventare un modello in Europa nell’attuazione del PNRR. Abbiamo ancora molto lavoro da fare, ma i risultati raggiunti finora ci rendono orgogliosi e ci spronano a fare sempre meglio. Nell’interesse dell’Italia e degli italiani.</t>
+  </si>
+  <si>
+    <t>Ieri sera ho visitato il Villaggio "Agricoltura È", un evento di grande valore che testimonia un impegno assunto da questo Governo fin dal suo insediamento: ridare dignità e centralità all’agricoltura e agli agricoltori. Un grazie sentito al Ministro Lollobrigida e al MASAF per aver dato vita a questa iniziativa così significativa e a tutti i partecipanti, alle associazioni e ai giovani, che con passione e competenza hanno messo in mostra l’eccellenza dei nostri prodotti e la forza della nostra tradizione.</t>
+  </si>
+  <si>
+    <t>In occasione del 208° anniversario di fondazione del Corpo della Polizia Penitenziaria, desidero inviare i miei migliori auguri alle donne e agli uomini in divisa che ogni giorno operano con senso di responsabilità e profonda dedizione, alle volte in complicate situazioni. A nome del Governo il più sincero ringraziamento per il vostro prezioso lavoro.</t>
+  </si>
+  <si>
+    <t>Felice di sapere che Papa Francesco stia tornando in Vaticano. A lui vanno un pensiero speciale e i migliori auguri, con affetto e gratitudine per il suo instancabile impegno e la sua guida preziosa.</t>
+  </si>
+  <si>
+    <t>Oggi è la Giornata della Memoria e dell'Impegno in ricordo delle vittime innocenti delle mafie, un importante momento di riflessione per tutti noi. L'Italia e le sue Istituzioni si inchinano davanti al sacrificio di chi ha perso la vita per mano della criminalità organizzata: cittadini onesti, servitori dello Stato, persone innocenti cadute sotto i colpi vigliacchi di un giogo vile e spietato. Le mafie sono un nemico dichiarato della nostra democrazia, un’offesa alla dignità della Nazione. Per questo, con assoluta determinazione e fermezza, ribadiamo la nostra condanna ad ogni tipo di mafia e ci impegniamo, ogni giorno, a combatterla. Onorare il sacrificio delle vittime significa agire per rafforzare la giustizia, garantire sicurezza, difendere la libertà di tutti i cittadini, rifiutare ed estirpare ogni forma di illegalità, violenza e sopraffazione. La loro memoria è, e sempre deve essere, la nostra guida.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Un augurio speciale a tutti quei papà che passano la notte insonni, cullando i propri neonati. A quelli che ogni mattina vestono i bambini con cura e li accompagnano all’asilo o a scuola. A quelli che si fanno in quattro per sostenere i propri figli e la propria famiglia. A quelli che li proteggono da lassù. A chi vive la dolcezza di una vita di coppia e a chi, con il suo amore, riesce a dare tutto anche da solo. A quelli che, ormai con i figli adulti, non smettono mai di preoccuparsi per loro. Grazie a ognuno di voi. Perché Papà e Mamma sono e rimarranno sempre le parole più belle del mondo. Buona </t>
+    </r>
+    <r>
+      <rPr>
+        <color rgb="FF000000"/>
+        <u/>
+      </rPr>
+      <t>#FestadelPapà</t>
+    </r>
+  </si>
+  <si>
+    <t>In diretta dal Senato della Repubblica, le comunicazioni in vista del prossimo Consiglio europeo.</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <color rgb="FF1155CC"/>
+        <u/>
+      </rPr>
+      <t>#17marzo</t>
+    </r>
+    <r>
+      <rPr/>
+      <t>, Giornata dell’Unità Nazionale, della Costituzione, dell’Inno e della Bandiera. Oggi celebriamo l’identità della Nazione, i valori che ci uniscono e il percorso che ha forgiato l’Italia. Quest’anno, questa ricorrenza assume un significato ancora più solenne: il Consiglio dei Ministri ha colmato una lacuna normativa di sette anni e ha approvato lo schema di decreto del Presidente della Repubblica che stabilisce le modalità di esecuzione dell'Inno nazionale - "Il Canto degli Italiani" scritto da Goffredo Mameli e musicato da Michele Novaro - nelle cerimonie istituzionali e pubbliche. Un doveroso atto di rispetto verso uno dei simboli più rappresentativi della Nazione e della storia d'Italia. Viva l’Italia, la nostra storia, la nostra Bandiera!</t>
+    </r>
+  </si>
+  <si>
+    <t>Rivolgo le mie congratulazioni a @MarkJCarney, nuovo Primo Ministro del Canada. Confido in una collaborazione sempre forte e dinamica tra le nostre Nazioni, legate da saldi rapporti bilaterali e unite quest’anno dal passaggio di testimone alla guida del G7.</t>
+  </si>
+  <si>
+    <t>Oggi ho avuto il piacere di incontrare gli straordinari atleti dei Giochi Mondiali Invernali Special Olympics Torino 2025. A tutti loro va il mio più sincero augurio: continuate a inseguire i vostri sogni con la stessa forza e il sorriso che ho visto oggi nei vostri occhi. L’Italia è con voi!</t>
+  </si>
+  <si>
+    <t>Il mio pensiero va alle popolazioni colpite dal maltempo che sta investendo diverse zone d’Italia, causando gravi danni e difficoltà ai cittadini. Un sentito ringraziamento a tutte le forze dell’ordine e ai soccorritori che, con impegno e professionalità, stanno prestando aiuto alle comunità colpite. Il Governo è al fianco delle popolazioni in difficoltà e garantirà ogni supporto necessario.</t>
+  </si>
+  <si>
+    <t>Sto monitorando costantemente l’evolversi della situazione a seguito della forte scossa di terremoto che ha colpito questa notte l’area dei Campi Flegrei. Sono in stretto contatto con il sottosegretario Alfredo Mantovano, con il Ministro per la Protezione Civile, Nello Musumeci, e con il Capo del Dipartimento della Protezione Civile, Fabio Ciciliano.</t>
+  </si>
+  <si>
+    <t>Esprimo il mio profondo cordoglio per le vittime dell’alluvione che ha colpito alcune città dell’Argentina. Il Governo italiano rinnova il proprio sostegno alle autorità argentine impegnate nei soccorsi e nell’assistenza alla popolazione coinvolta.</t>
+  </si>
+  <si>
+    <t>Coraggiose, instancabili, determinate: le donne sono il cuore pulsante della nostra società. Ogni giorno, con forza, talento e dedizione, costruiscono, innovano e ispirano. Come Governo, il nostro impegno è garantire a ogni donna le opportunità per essere protagonista in ogni settore, senza ostacoli. I numeri parlano chiaro: l’occupazione femminile ha raggiunto il livello più alto di sempre, superando i dieci milioni di donne lavoratrici. Un risultato importante, ma sappiamo che molto resta da fare per una parità piena in ogni ambito. Le donne non devono più scegliere tra carriera e vita privata. La parità significa assicurare a tutte le donne le condizioni per realizzarsi pienamente, senza sacrificare né il lavoro né la vita familiare. Continueremo a lavorare per creare le opportunità che permettano a ogni donna di esprimere il proprio potenziale al massimo, senza limiti e senza barriere.</t>
+  </si>
+  <si>
+    <t>Voglio esprimere profonda gratitudine ai @vigilidelfuoco che, dopo più di 24 ore di fatica senza mai arrendersi, sono riusciti a salvare la donna rimasta sotto le macerie del palazzo crollato in via de Amicis a Bari. Grazie per essere sempre pronti a tendere una mano a chi si trova nelle situazioni più complicate, eroi.</t>
+  </si>
+  <si>
+    <t>Le Sezioni Unite della Corte di Cassazione hanno condannato il governo a risarcire un gruppo di immigrati illegali trasportati dalla nave Diciotti perché il governo di allora, con Ministro dell’Interno Matteo Salvini, non li fece sbarcare immediatamente in Italia. Lo fanno affermando un principio risarcitorio assai opinabile, quello della presunzione del danno, in contrasto con la giurisprudenza consolidata e con le conclusioni del Procuratore Generale. In sostanza, per effetto di questa decisione, il Governo dovrà risarcire – con i soldi dei cittadini italiani onesti che pagano le tasse – persone che hanno tentato di entrare in Italia illegalmente, ovvero violando la legge dello Stato italiano. Non credo siano queste le decisioni che avvicinano i cittadini alle istituzioni, e confesso che dover spendere soldi per questo, quando non abbiamo abbastanza risorse per fare tutto quello che sarebbe giusto fare, è molto frustrante.</t>
+  </si>
+  <si>
+    <t>Hai dato voce alle notti magiche azzurre, accompagnando milioni di italiani con competenza e passione, come un grande compagno d’avventure. Sei stato la voce storica del calcio italiano, un’icona intramontabile del giornalismo sportivo, destinata a rimanere per sempre nella storia dello sport e nei cuori di tutti noi. Ciao, Bruno Pizzul</t>
+  </si>
+  <si>
+    <t>Secondo i dati diffusi oggi dall’Istat, a gennaio 2025 il numero di occupati in Italia ha raggiunto quota 24 milioni 222mila. Il tasso di occupazione cresce al 62,8%. Su base annua, l’occupazione aumenta del 2,2%, con 513mila occupati in più. Numeri importanti, che confermano la crescita dell’occupazione e il buon andamento del mercato del lavoro. Ma sappiamo che possiamo e dobbiamo fare ancora di più. Proseguiremo con determinazione su questa strada, per consolidare la crescita e rafforzare la competitività dell’Italia.</t>
+  </si>
+  <si>
+    <t>Buongiorno. Per chi se la fosse persa, ripropongo la mia intervista a “XXI Secolo” di ieri sera.</t>
+  </si>
+  <si>
+    <t>Esprimo il mio cordoglio per quanto accaduto a Mannheim. La nostra vicinanza alle persone colpite e ai loro cari, i migliori auguri ai feriti e piena solidarietà alla Germania tutta. I tentativi di destabilizzare le Nazioni democratiche non prevarranno ed è nostro impegno tenere alta la guardia contro qualunque forma di violenza.</t>
+  </si>
+  <si>
+    <t>Il ricevitore LuGRE, simbolo dell’eccellenza tecnologica spaziale italiana, ha raggiunto la Luna a bordo del lander Blue Ghost. Festeggiamo un grande successo, frutto di una straordinaria sinergia tra pubblico e privato - in particolare tra ASI, Qascom e Politecnico di Torino - che rafforza il ruolo di primo piano dell'Italia nel panorama spaziale internazionale. Il Governo continuerà a sostenere lo sviluppo del settore spaziale, l’innovazione e la ricerca, per garantire all'Italia ambiziosi traguardi, confermando la vocazione italiana a farsi promotrice di eccellenza e progresso nel mondo.</t>
+  </si>
+  <si>
+    <t>Oggi stanziamo 3 miliardi per fronteggiare il caro bollette e sostenere cittadini, famiglie e imprese. Ascoltate cosa prevede l’intervento del Governo.</t>
+  </si>
+  <si>
+    <t>86 anni fa nasceva il Corpo Nazionale dei Vigili del Fuoco. Uomini e donne di grande coraggio e preparazione, che rappresentano una risorsa fondamentale nel soccorso alle popolazioni e nei diversi scenari emergenziali. Eccellenza stimata in tutto il mondo, a loro desidero inviare i miei auguri per questa giornata così significativa, insieme al plauso e alla riconoscenza per l'inestimabile impegno quotidiano.</t>
+  </si>
+  <si>
+    <t>Salvo D’Acquisto è un eroe, simbolo di coraggio, sacrificio e dedizione al dovere. La decisione del Santo Padre di autorizzare il percorso per la sua beatificazione è un riconoscimento straordinario per un uomo che ha dato la vita per salvare quella di altri, incarnando i valori più alti di umanità e servizio. Il suo esempio resterà per sempre vivo nella memoria della nostra Nazione.</t>
+  </si>
+  <si>
+    <t>Grazie a Donald Trump per le sue parole. Italia, Stati Uniti ed Europa condividono valori e responsabilità comuni. Lavoreremo insieme per affrontare le sfide globali con determinazione e visione.</t>
+  </si>
+  <si>
+    <t>Accolgo con grande soddisfazione la decisione degli Emirati Arabi Uniti di investire 40 miliardi di dollari in Italia. Si tratta di uno degli investimenti esteri più significativi nella storia della nostra Nazione, una straordinaria dimostrazione di fiducia nell’Italia e nella solidità della nostra economia. Abbiamo scelto di sviluppare questa collaborazione lungo diversi assi strategici: dall’intelligenza artificiale ai data center, dal dominio subacqueo alla ricerca spaziale, dalle energie rinnovabili alle terre rare. Oggi è una giornata importante per l’Italia e per gli Emirati. Abbiamo scritto una nuova, straordinaria pagina della nostra storia comune e ci apprestiamo a tracciarne molte altre. Lo faremo nel segno dell’amicizia che ci unisce, ma soprattutto con l’obiettivo di garantire benessere e prosperità ai nostri popoli.</t>
+  </si>
+  <si>
+    <t>Il mio intervento al Forum imprenditoriale Italia-Emirati Arabi Uniti</t>
+  </si>
+  <si>
+    <t>Profondo cordoglio per la tragica scomparsa di Francesco Occhiuto, figlio del senatore Mario Occhiuto e nipote del Presidente della Regione Calabria Roberto Occhiuto. In questo momento di grande dolore desidero inviare la mia più sentita vicinanza a tutta la loro famiglia e ai loro cari.</t>
+  </si>
+  <si>
+    <t>Sono sconcertata per la sentenza di condanna del Sottosegretario Andrea Delmastro, per il quale il pubblico ministero aveva inizialmente richiesto l’archiviazione e successivamente l’assoluzione. Mi chiedo se il giudizio sia realmente basato sul merito della questione. Il Sottosegretario Delmastro rimane al suo posto.</t>
+  </si>
+  <si>
+    <t>Voglio condividere con voi una buona notizia sul lavoro del Governo nel contrasto all’evasione fiscale. Ascoltate.</t>
+  </si>
+  <si>
+    <t>Congratulazioni e auguri di buon lavoro a Daniela Fumarola, neosegretaria generale della @CislNazionale. Sono fiduciosa di poter consolidare insieme il dialogo e la cooperazione già esistente tra il Governo e una delle più importanti organizzazione del lavoro della nostra Nazione, nel rispetto dei rispettivi ruoli e nell'esclusivo interesse di cittadini, lavoratori e imprese.
+Colgo l'occasione per ringraziare nuovamente il segretario uscente Luigi Sbarra per quanto profuso in questi anni e per essersi sempre dimostrato un interlocutore serio, sincero e risoluto.</t>
+  </si>
+  <si>
+    <t>L’Inno di Mameli è il canto di un popolo che ha lottato per la sua libertà e la sua unità. Ogni parola racchiude la nostra storia, il nostro orgoglio, il nostro senso di appartenenza. “Fratelli d’Italia” è un richiamo all’identità e alla fratellanza di una Nazione che guarda avanti con fierezza. Viva l’Italia, viva il nostro Inno.</t>
+  </si>
+  <si>
+    <t>Un’operazione straordinaria dei Carabinieri del Comando Provinciale di Palermo ha portato oggi all’arresto di oltre 180 persone, tra cui diversi boss, infliggendo un colpo durissimo a Cosa Nostra. Un risultato che conferma l’impegno incessante dello Stato nella lotta alla criminalità organizzata. Le intercettazioni lo dicono chiaramente: “L’Italia per noi è diventata scomoda, io me ne devo andare”, ammetteva uno degli arrestati. Un segnale chiaro: la criminalità organizzata è alle strette, la lotta alla mafia non si ferma e non si fermerà. Grazie ai Carabinieri del Nucleo Investigativo e a tutte le Forze dell’Ordine che ogni giorno difendono la legalità e la sicurezza dei cittadini. La mafia va sconfitta con determinazione e senza alcun compromesso. Lo Stato c’è e non arretra.</t>
+  </si>
+  <si>
+    <t>Le parole del Vice Ispettore Christian Di Martino della Polizia di Stato, accoltellato alla stazione di Lambrate (Milano), raccontano perfettamente il valore e il sacrificio di chi, ogni giorno, difende la nostra sicurezza, anche a costo della propria vita. L’Italia è con te, Christian, e con tutti gli uomini e le donne in divisa che, con coraggio, dedizione e senso del dovere, proteggono i cittadini. Grazie.</t>
+  </si>
+  <si>
+    <t>Nel Giorno del Ricordo rendiamo omaggio alle vittime delle foibe e a tutti coloro che subirono la tragedia dell’esodo giuliano-dalmata, una pagina dolorosa della nostra storia per troppo tempo dimenticata. Ricordare è un dovere di verità e giustizia, per onorare chi ha sofferto e trasmettere questa memoria alle nuove generazioni. L’Italia non dimentica.</t>
+  </si>
+  <si>
+    <t>La Foiba di Basovizza è un luogo sacro, un monumento nazionale, da onorare con il silenzio e con la preghiera. Oltraggiare Basovizza, per di più con scritte ripugnanti che richiamano a pagine drammatiche della nostra storia, non vuol dire solo calpestare la memoria dei martiri delle foibe ma significa oltraggiare la Nazione intera. Ciò che è accaduto è un atto di gravità inaudita, che non può restare impunito.</t>
+  </si>
+  <si>
+    <t>Non sarà certo qualche polemica forzata e strumentale a scalfire il nostro rapporto. Con Matteo Salvini abbiamo affrontato tante battaglie insieme e continueremo a lavorare fianco a fianco, con lealtà e determinazione, per il bene dell’Italia. La stima nei suoi confronti è nei fatti: oltre a essere Ministro delle Infrastrutture e dei Trasporti, è anche Vicepremier del nostro Governo. Un ruolo centrale per portare avanti le riforme e i progetti che servono alla Nazione. Noi andiamo avanti, compatti, come sempre.</t>
+  </si>
+  <si>
+    <t>Esprimo totale solidarietà ai due agenti aggrediti a martellate in una stazione di servizio nei pressi di Torino. Seguo con apprensione gli aggiornamenti del loro stato di salute e voglio ribadire la massima gratitudine a tutte le nostre Forze dell'Ordine che ogni giorno presidiano il territorio e difendono la sicurezza dei cittadini. Rischiando anche sulla propria pelle, con senso di appartenenza, altruismo e sacrificio, dovendo subire a volte anche ingiuste campagne denigratorie di chi vorrebbe delegittimare l'autorità che rappresentano. Non dimentichiamolo, mai.</t>
+  </si>
+  <si>
+    <t>Esprimo la mia vicinanza al Governo e al popolo svedese per il terribile attacco che ha colpito la città di Örebro. Il mio pensiero va alle vittime, alle loro famiglie e a tutti i feriti coinvolti. Non possiamo accettare che violenza e barbarie trovino spazio nelle nostre società.</t>
+  </si>
+  <si>
+    <t>L’inchiesta della DDA di Salerno, che ha portato a 36 indagati e svelato oltre 2mila richieste false di permessi di soggiorno, conferma ancora una volta quanto denunciato dal Governo: per anni, la gestione dei flussi migratori è stata terreno fertile per criminali senza scrupoli. Un sistema che speculava sull’immigrazione, sfruttando cittadini stranieri disposti a pagare pur di ottenere un permesso di soggiorno e alimentando un giro d’affari illecito da milioni di euro. Non a caso, abbiamo deciso di rafforzare i controlli per impedire che le quote di ingresso regolare finiscano nelle mani di chi sfrutta l’immigrazione per fare affari. E non a caso, ho presentato un esposto all’Antimafia per fare luce sulle troppe anomalie di questo sistema. L’immigrazione non può essere lasciata in balìa della criminalità. Continueremo a lavorare per ristabilire regole serie e legalità.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Congratulazioni e auguri di buon lavoro all'amico @Bart_DeWever, nuovo Primo Ministro del Regno del Belgio. Certa che lavoreremo insieme guidati da valori e obiettivi comuni, sia a livello bilaterale che nell'affrontare le importanti sfide che ci attendono in ambito europeo e internazionale.
+</t>
+  </si>
+  <si>
+    <t>Mentre il Governo lavora senza sosta per portare risultati all’Italia, c’è chi prova invano a smontarli. E intanto il mondo torna a puntare su di noi.</t>
+  </si>
+  <si>
+    <t>Agli italiani dico, ancora una volta: finché ci siete voi ci sarò anche io. E non intendo mollare di un centimetro.</t>
+  </si>
+  <si>
+    <t>Ora in videocollegamento con Nicola Porro per l'ottava edizione de “La Ripartenza”. Collegatevi!</t>
+  </si>
+  <si>
+    <t>Il 2024 segna un altro importante traguardo per l’Italia: con oltre 305 miliardi di export, raggiungiamo il valore più alto degli ultimi dieci anni. Un segno positivo della forza del nostro sistema produttivo e della competitività globale. Un’Italia sempre più forte e protagonista nel mondo.</t>
+  </si>
+  <si>
+    <t>Il nostro impegno per difendere l’Italia proseguirà, come sempre, con determinazione e senza esitazioni. Quando sono in gioco la sicurezza della Nazione e l’interesse degli italiani, non esiste spazio per passi indietro. Dritti per la nostra strada.</t>
+  </si>
+  <si>
+    <t>Vale oggi quello che valeva ieri: non sono ricattabile e non mi faccio intimidire. Avanti a testa alta!</t>
+  </si>
+  <si>
+    <t>Un grande Jannik #Sinner trionfa agli #AusOpen 2025, difendendo il titolo conquistato l’anno scorso. Terzo Slam per lui che, non solo arricchisce il suo palmarès personale, ma rappresenta anche un motivo di grande orgoglio per l’Italia. Bravissimo</t>
+  </si>
+  <si>
+    <t>Oggi a Gedda ho avuto il piacere e l’onore di portare il saluto dell’Italia all’equipaggio dell’Amerigo Vespucci, la storica nave della Marina Militare italiana impegnata nel suo tour mondiale. Una straordinaria impresa che porta lustro alla nostra Nazione e ci rende profondamente orgogliosi. Viva la Marina Militare, viva l’Amerigo Vespucci, viva l’Italia!</t>
+  </si>
+  <si>
+    <t>Vi ripropongo il mio punto stampa di poco fa</t>
+  </si>
+  <si>
+    <t>Accolgo con grande soddisfazione i dati diffusi oggi dall’Istat sulla crescita dell’agricoltura italiana nel 2024. L’Italia si attesta come la Nazione tra i 27 Paesi della UE con il più alto valore aggiunto agricolo. È un primato storico che ci rende particolarmente orgogliosi e che è frutto del lavoro, della dedizione e della determinazione delle imprese e dei lavoratori del comparto. E siamo altrettanto fieri di aver sempre fatto la nostra parte per raggiungere quest’obiettivo. Il Governo, fin dal suo insediamento, ha rimesso al centro l’agricoltura, ha dedicato stanziamenti record e adottato politiche di sistema per promuovere e rilanciare il settore agroalimentare italiano e le nostre eccellenze. La strada intrapresa è quella giusta, e continueremo a lavorare in questa direzione.</t>
+  </si>
+  <si>
+    <t>Il nostro sentito ringraziamento agli investigatori della Squadra Mobile della Questura di Cosenza per aver ritrovato e riportato ai genitori la neonata rapita in ospedale. Un plauso ai nostri uomini e donne in divisa per lo straordinario lavoro di squadra e di ricerca. Un abbraccio alla mamma e al papà e un augurio di buona vita alla piccola Sofia!</t>
+  </si>
+  <si>
+    <t>Sono addolorata per la scomparsa di Luca Beatrice, uno dei più importanti e apprezzati critici d'arte italiani e presidente della Quadriennale di Roma. Perdiamo un uomo di grande intelligenza e cultura, la cui impronta rimarrà nel cuore e negli occhi di tanti. Sentite condoglianze a sua moglie Elisa, ai figli e alla famiglia. Riposi in pace.</t>
+  </si>
+  <si>
+    <t>Auguri di buon lavoro al Presidente @realDonaldTrump per l’inizio del suo nuovo mandato alla guida degli Stati Uniti d’America. Sono certa che l’amicizia tra le nostre Nazioni e i valori che ci uniscono continueranno a rafforzare la collaborazione tra Italia e USA, affrontando insieme le sfide globali e costruendo un futuro di prosperità e sicurezza per i nostri popoli.
+L’Italia sarà sempre impegnata nel consolidare il dialogo tra Stati Uniti ed Europa, quale pilastro essenziale per la stabilità e la crescita delle nostre comunità.</t>
+  </si>
+  <si>
+    <t>Nel giorno della nascita di Paolo Borsellino desidero ricordare un grande uomo, un giudice e un Servitore dello Stato che ci ha insegnato che avere paura è umano ma ciò che è importante è affiancare alla paura il coraggio. Il coraggio di combattere per quello in cui si crede e fare tutto ciò che è possibile per migliorare le cose. 
+Fin dall’insediamento del Governo abbiamo messo tra le nostre priorità la battaglia contro le mafie e, nel nome di Paolo Borsellino, di Giovanni Falcone e di tutti coloro che sono caduti per mano della criminalità organizzata, continueremo su questa strada per portare legalità e sicurezza, libertà e giustizia.
+Buon compleanno Paolo, il tuo esempio vive nelle nostre azioni.</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="3">
+  <fonts count="5">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -191,6 +698,14 @@
       <name val="Arial"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <color rgb="FF000000"/>
+    </font>
+    <font>
+      <u/>
+      <color rgb="FF0000FF"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -206,7 +721,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -214,6 +729,12 @@
       <alignment readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -679,7 +1200,762 @@
         <v>49</v>
       </c>
     </row>
+    <row r="51">
+      <c r="A51" s="1" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="1" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="1" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="1" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="1" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="1" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="1" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="1" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="1" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="1" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="1" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="1" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="1" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="1" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="2" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="1" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="1" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="1" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="2" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="2" t="s">
+        <v>79</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="1" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="1" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="1" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="1" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="2" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="s">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="1" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="1" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="1" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="3" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="s">
+        <v>116</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="2" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="3" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="4" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="2" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="2" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="2" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="2" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" s="2" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" s="2" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" s="2" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" s="1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" s="1" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" s="1" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" s="1" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" s="1" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" s="1" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" s="2" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" s="1" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" s="1" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" s="1" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" s="1" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" s="1" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" s="2" t="s">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" s="1" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" s="1" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" s="1" t="s">
+        <v>199</v>
+      </c>
+    </row>
   </sheetData>
-  <drawing r:id="rId1"/>
+  <hyperlinks>
+    <hyperlink r:id="rId1" ref="A116"/>
+    <hyperlink r:id="rId2" ref="A151"/>
+    <hyperlink r:id="rId3" ref="A153"/>
+  </hyperlinks>
+  <drawing r:id="rId4"/>
 </worksheet>
 </file>